--- a/temporario/Apontamento_Mateus.xlsx
+++ b/temporario/Apontamento_Mateus.xlsx
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="M2" s="75" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="N2" s="37" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="Q2" s="76" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R2" s="26" t="n"/>
@@ -1480,17 +1480,17 @@
     <row r="4">
       <c r="A4" s="80" t="inlineStr">
         <is>
-          <t>FAT27902888</t>
+          <t>FAT27810133</t>
         </is>
       </c>
       <c r="B4" s="81" t="inlineStr">
         <is>
-          <t>26/02299</t>
+          <t>26/02353</t>
         </is>
       </c>
       <c r="C4" s="82" t="inlineStr">
         <is>
-          <t>SENIR</t>
+          <t>MARCIO RODRIGO TRANSPORTE</t>
         </is>
       </c>
       <c r="D4" s="83" t="n"/>
@@ -1517,23 +1517,23 @@
     <row r="5">
       <c r="A5" s="86" t="inlineStr">
         <is>
-          <t>FAT27467253</t>
+          <t>FAT27909550</t>
         </is>
       </c>
       <c r="B5" s="87" t="inlineStr">
         <is>
-          <t>26/02417</t>
+          <t>26/02244</t>
         </is>
       </c>
       <c r="C5" s="76" t="inlineStr">
         <is>
-          <t>CARTHOM'S</t>
+          <t>FARMABASE</t>
         </is>
       </c>
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="76" t="inlineStr">
         <is>
-          <t>8,5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" s="26" t="n"/>
@@ -1552,27 +1552,11 @@
       <c r="S5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAT27896111 </t>
-        </is>
-      </c>
-      <c r="B6" s="87" t="inlineStr">
-        <is>
-          <t>26/02411</t>
-        </is>
-      </c>
-      <c r="C6" s="76" t="inlineStr">
-        <is>
-          <t>DENTSPLY IND</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="45" t="n"/>
       <c r="D6" s="26" t="n"/>
-      <c r="E6" s="76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="E6" s="45" t="n"/>
       <c r="F6" s="26" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
@@ -1589,27 +1573,11 @@
       <c r="S6" s="18" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="86" t="inlineStr">
-        <is>
-          <t>FAT26744158</t>
-        </is>
-      </c>
-      <c r="B7" s="87" t="inlineStr">
-        <is>
-          <t>26/02187</t>
-        </is>
-      </c>
-      <c r="C7" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ECOBOXES </t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="45" t="n"/>
       <c r="D7" s="26" t="n"/>
-      <c r="E7" s="76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="E7" s="45" t="n"/>
       <c r="F7" s="26" t="n"/>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>

--- a/temporario/Apontamento_Mateus.xlsx
+++ b/temporario/Apontamento_Mateus.xlsx
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="M2" s="75" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="N2" s="37" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="Q2" s="76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R2" s="26" t="n"/>
@@ -1480,17 +1480,17 @@
     <row r="4">
       <c r="A4" s="80" t="inlineStr">
         <is>
-          <t>FAT27810133</t>
+          <t>FAT27902888</t>
         </is>
       </c>
       <c r="B4" s="81" t="inlineStr">
         <is>
-          <t>26/02353</t>
+          <t>26/02299</t>
         </is>
       </c>
       <c r="C4" s="82" t="inlineStr">
         <is>
-          <t>MARCIO RODRIGO TRANSPORTE</t>
+          <t>SENIR</t>
         </is>
       </c>
       <c r="D4" s="83" t="n"/>
@@ -1517,23 +1517,23 @@
     <row r="5">
       <c r="A5" s="86" t="inlineStr">
         <is>
-          <t>FAT27909550</t>
+          <t>FAT27467253</t>
         </is>
       </c>
       <c r="B5" s="87" t="inlineStr">
         <is>
-          <t>26/02244</t>
+          <t>26/02417</t>
         </is>
       </c>
       <c r="C5" s="76" t="inlineStr">
         <is>
-          <t>FARMABASE</t>
+          <t>CARTHOM'S</t>
         </is>
       </c>
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8,5</t>
         </is>
       </c>
       <c r="F5" s="26" t="n"/>
@@ -1552,11 +1552,27 @@
       <c r="S5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="24" t="n"/>
-      <c r="C6" s="45" t="n"/>
+      <c r="A6" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAT27896111 </t>
+        </is>
+      </c>
+      <c r="B6" s="87" t="inlineStr">
+        <is>
+          <t>26/02411</t>
+        </is>
+      </c>
+      <c r="C6" s="76" t="inlineStr">
+        <is>
+          <t>DENTSPLY IND</t>
+        </is>
+      </c>
       <c r="D6" s="26" t="n"/>
-      <c r="E6" s="45" t="n"/>
+      <c r="E6" s="76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="F6" s="26" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
@@ -1573,11 +1589,27 @@
       <c r="S6" s="18" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="24" t="n"/>
-      <c r="C7" s="45" t="n"/>
+      <c r="A7" s="86" t="inlineStr">
+        <is>
+          <t>FAT26744158</t>
+        </is>
+      </c>
+      <c r="B7" s="87" t="inlineStr">
+        <is>
+          <t>26/02187</t>
+        </is>
+      </c>
+      <c r="C7" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ECOBOXES </t>
+        </is>
+      </c>
       <c r="D7" s="26" t="n"/>
-      <c r="E7" s="45" t="n"/>
+      <c r="E7" s="76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="F7" s="26" t="n"/>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
